--- a/data/Skin care creators.xlsx
+++ b/data/Skin care creators.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N454"/>
+  <dimension ref="A1:Y511"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="65.25" customWidth="1" style="16" min="1" max="1"/>
@@ -9227,8 +9227,419 @@
         </is>
       </c>
     </row>
-    <row r="453"/>
-    <row r="454"/>
+    <row r="453">
+      <c r="A453" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kareenatekwani/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glowwithaashi_/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glow_withsandy/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_anjali_skin_kochi/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sneha_skincare_vizag/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mysore_skin_lab/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tanvi_skin_nagpur/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_rutu_dermat_vadodara/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bhubaneswar_skincare_diaries/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/siliguri_skin_review/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/udaipur_dermat_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_manjot_skin_chd/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ludhiana_derma_tips/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lucknow_skin_doctor/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/varanasi_skin_wellness/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dehradun_skin_health/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_shafna_derma_calicut/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/madurai_skin_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rajkot_skin_diaries/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ambala_skin_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jodhpur_skin_review/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/agra_skin_doctor/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/patna_skin_journal/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ranchi_skin_diaries/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/raipur_derma_tips/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kolhapur_skin_wellness/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ajmer_skin_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jalandhar_skin_journal/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bhopal_derma_tips/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nashik_skin_wellness/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cuttack_skin_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kanpur_derma_tips/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vijayawada_skin_wellness/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gwalior_skin_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jabalpur_skin_health/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_varun_derma_thrissur/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mangalore_skin_diaries/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/belgaum_skin_wellness/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hubli_derma_tips/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tirupati_skin_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/salem_skin_wellness/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/aligarh_derma_tips/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/guwahati_skin_lab/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shillong_skin_health/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bareilly_skin_diaries/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gorakhpur_skin_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rohtak_derma_tips/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/panipat_skin_health/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/karnal_skin_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bathinda_skin_diaries/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ujjain_skin_wellness/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kota_skin_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bikaner_derma_tips/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dhanbad_skin_wellness/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jamshedpur_skin_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_fathima_skin_kannur/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kollam_skin_diaries/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alappuzha_skin_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/palakkad_skin_wellness/reels/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="H323:I323"/>
@@ -9699,6 +10110,65 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A449" r:id="rId447"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A451" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A452" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A453" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A454" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A455" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A456" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A457" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A458" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A459" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A460" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A461" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A462" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A463" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A464" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A465" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A466" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A467" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A468" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A469" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A470" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A471" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A472" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A473" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A474" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A475" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A476" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A477" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A478" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A479" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A480" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A481" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A482" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A483" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A484" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A485" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A486" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A487" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A488" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A489" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A490" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A491" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A492" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A493" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A494" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A495" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A496" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A497" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A498" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A499" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A500" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A501" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A502" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A503" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A504" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A505" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A506" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A507" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A508" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A509" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A510" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A511" r:id="rId508"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Skin care creators.xlsx
+++ b/data/Skin care creators.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -77,6 +77,12 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001155CC"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -98,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -142,6 +148,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,7 +448,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y511"/>
+  <dimension ref="A1:N460"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="65.25" customWidth="1" style="16" min="1" max="1"/>
@@ -9214,429 +9223,72 @@
       <c r="N450" s="15" t="n"/>
     </row>
     <row r="451">
-      <c r="A451" s="10" t="inlineStr">
+      <c r="A451" s="17" t="inlineStr">
         <is>
           <t>https://www.instagram.com/skinnbydeepanshu/reels/</t>
         </is>
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="10" t="inlineStr">
+      <c r="A452" s="17" t="inlineStr">
         <is>
           <t>https://www.instagram.com/dr.nisha.mavani/reels/</t>
         </is>
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/kareenatekwani/reels/</t>
+      <c r="A453" s="17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kareena.t/reels/</t>
         </is>
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="10" t="inlineStr">
+      <c r="A454" s="17" t="inlineStr">
         <is>
           <t>https://www.instagram.com/glowwithaashi_/reels/</t>
         </is>
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="10" t="inlineStr">
+      <c r="A455" s="17" t="inlineStr">
         <is>
           <t>https://www.instagram.com/glow_withsandy/reels/</t>
         </is>
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/dr_anjali_skin_kochi/reels/</t>
+      <c r="A456" s="17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/simplymystyle_unni/reels/</t>
         </is>
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/sneha_skincare_vizag/reels/</t>
+      <c r="A457" s="17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drpriticadermatology/reels/</t>
         </is>
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/mysore_skin_lab/reels/</t>
+      <c r="A458" s="17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/calmcarejourney/reels/</t>
         </is>
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/tanvi_skin_nagpur/reels/</t>
+      <c r="A459" s="17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/skinstoriesbydrsangeeta/reels/</t>
         </is>
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/dr_rutu_dermat_vadodara/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/bhubaneswar_skincare_diaries/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/siliguri_skin_review/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/udaipur_dermat_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/dr_manjot_skin_chd/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/ludhiana_derma_tips/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/lucknow_skin_doctor/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/varanasi_skin_wellness/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/dehradun_skin_health/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/dr_shafna_derma_calicut/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/madurai_skin_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/rajkot_skin_diaries/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/ambala_skin_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jodhpur_skin_review/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/agra_skin_doctor/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/patna_skin_journal/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/ranchi_skin_diaries/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/raipur_derma_tips/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/kolhapur_skin_wellness/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/ajmer_skin_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jalandhar_skin_journal/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/bhopal_derma_tips/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nashik_skin_wellness/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/cuttack_skin_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/kanpur_derma_tips/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/vijayawada_skin_wellness/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/gwalior_skin_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jabalpur_skin_health/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/dr_varun_derma_thrissur/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/mangalore_skin_diaries/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/belgaum_skin_wellness/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/hubli_derma_tips/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/tirupati_skin_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/salem_skin_wellness/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/aligarh_derma_tips/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/guwahati_skin_lab/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/shillong_skin_health/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/bareilly_skin_diaries/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/gorakhpur_skin_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/rohtak_derma_tips/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/panipat_skin_health/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/karnal_skin_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/bathinda_skin_diaries/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/ujjain_skin_wellness/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/kota_skin_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/bikaner_derma_tips/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/dhanbad_skin_wellness/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jamshedpur_skin_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/dr_fathima_skin_kannur/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/kollam_skin_diaries/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/alappuzha_skin_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" s="10" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/palakkad_skin_wellness/reels/</t>
+      <c r="A460" s="17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/himanshi_freshfacebeauty/reels/</t>
         </is>
       </c>
     </row>
@@ -10118,57 +9770,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A458" r:id="rId455"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A459" r:id="rId456"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A460" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A461" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A462" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A463" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A464" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A465" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A466" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A467" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A468" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A469" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A470" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A471" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A472" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A473" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A474" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A475" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A476" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A477" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A478" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A479" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A480" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A481" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A482" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A483" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A484" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A485" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A486" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A487" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A488" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A489" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A490" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A491" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A492" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A493" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A494" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A495" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A496" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A497" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A498" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A499" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A500" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A501" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A502" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A503" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A504" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A505" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A506" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A507" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A508" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A509" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A510" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A511" r:id="rId508"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Skin care creators.xlsx
+++ b/data/Skin care creators.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -83,6 +83,12 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001155CC"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -104,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -151,6 +157,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,7 +455,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N460"/>
+  <dimension ref="A1:N512"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="65.25" customWidth="1" style="16" min="1" max="1"/>
@@ -9289,6 +9296,370 @@
       <c r="A460" s="17" t="inlineStr">
         <is>
           <t>https://www.instagram.com/himanshi_freshfacebeauty/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drhitasha_patil/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_vandana_skindoc/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drsheenamskincare/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr.yashaswii/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beautypost.in/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bolt_officiall/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dermaplusdrunnati/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr.krishna_dermatologist/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr.ambar.derma/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr.bharatipanda/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drpartha_dermatologist/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/theharshitam/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/blushingwink_/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/suhanixo_/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glowwithitrat/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/itsdeekshithaaaa/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shruti_saini12/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ummukulzu_azar/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vaishalikumari/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mezzystories/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the_unapologetic_dermatologist/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_mahima_1109/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/apoorwa_vaish__/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shanika.khurmi/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/blissbydrshikhaaggarwal/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drsheenapandey_md/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drvivekchoudharydermatologist/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr.animesh_saxena/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drpriyanksen/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr.rachiswayatagupta/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beautifulspotlessskin/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr.ayushipandeysharma/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nehamathew/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_sasi_k_attili/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr.ushmakantamuneni/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drjyothidermatologist/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/twacha_drsuman/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/preetimehta._/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_namita_.3/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_anushka_9142/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yourgirlsupernova/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rasna.bharadwaj/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr.dermarosh/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_drpriyankaderm/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drpratiksheth.mdskin/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drsnehagupta_md/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cosmetiquebydrsimratsandhu/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drjenny.lsc/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dermadr_priya/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr.vivekanandh_dermatologist/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drsunilkothiwalamd/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_atul_kathed/reels/</t>
         </is>
       </c>
     </row>
@@ -9770,6 +10141,58 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A458" r:id="rId455"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A459" r:id="rId456"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A460" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A461" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A462" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A463" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A464" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A465" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A466" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A467" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A468" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A469" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A470" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A471" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A472" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A473" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A474" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A475" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A476" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A477" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A478" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A479" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A480" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A481" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A482" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A483" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A484" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A485" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A486" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A487" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A488" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A489" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A490" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A491" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A492" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A493" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A494" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A495" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A496" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A497" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A498" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A499" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A500" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A501" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A502" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A503" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A504" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A505" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A506" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A507" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A508" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A509" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A510" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A511" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A512" r:id="rId509"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Skin care creators.xlsx
+++ b/data/Skin care creators.xlsx
@@ -110,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -158,6 +158,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9230,72 +9233,72 @@
       <c r="N450" s="15" t="n"/>
     </row>
     <row r="451">
-      <c r="A451" s="17" t="inlineStr">
+      <c r="A451" s="19" t="inlineStr">
         <is>
           <t>https://www.instagram.com/skinnbydeepanshu/reels/</t>
         </is>
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="17" t="inlineStr">
+      <c r="A452" s="19" t="inlineStr">
         <is>
           <t>https://www.instagram.com/dr.nisha.mavani/reels/</t>
         </is>
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="17" t="inlineStr">
+      <c r="A453" s="19" t="inlineStr">
         <is>
           <t>https://www.instagram.com/kareena.t/reels/</t>
         </is>
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="17" t="inlineStr">
+      <c r="A454" s="19" t="inlineStr">
         <is>
           <t>https://www.instagram.com/glowwithaashi_/reels/</t>
         </is>
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="17" t="inlineStr">
+      <c r="A455" s="19" t="inlineStr">
         <is>
           <t>https://www.instagram.com/glow_withsandy/reels/</t>
         </is>
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="17" t="inlineStr">
+      <c r="A456" s="19" t="inlineStr">
         <is>
           <t>https://www.instagram.com/simplymystyle_unni/reels/</t>
         </is>
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="17" t="inlineStr">
+      <c r="A457" s="19" t="inlineStr">
         <is>
           <t>https://www.instagram.com/drpriticadermatology/reels/</t>
         </is>
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="17" t="inlineStr">
+      <c r="A458" s="19" t="inlineStr">
         <is>
           <t>https://www.instagram.com/calmcarejourney/reels/</t>
         </is>
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="17" t="inlineStr">
+      <c r="A459" s="19" t="inlineStr">
         <is>
           <t>https://www.instagram.com/skinstoriesbydrsangeeta/reels/</t>
         </is>
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="17" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/himanshi_freshfacebeauty/reels/</t>
+      <c r="A460" s="19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drparwaazmatharoo/reels/</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9515,7 @@
     <row r="491">
       <c r="A491" s="18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beautifulspotlessskin/reels/</t>
+          <t>https://www.instagram.com/dr.mamtavijay/reels/</t>
         </is>
       </c>
     </row>
@@ -9561,21 +9564,21 @@
     <row r="498">
       <c r="A498" s="18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/preetimehta._/reels/</t>
+          <t>https://www.instagram.com/dr.manjot_md_dermatologist/reels/</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_namita_.3/reels/</t>
+          <t>https://www.instagram.com/drpriyas_enhance/reels/</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_anushka_9142/reels/</t>
+          <t>https://www.instagram.com/tanishachawlaa/reels/</t>
         </is>
       </c>
     </row>
@@ -9589,7 +9592,7 @@
     <row r="502">
       <c r="A502" s="18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rasna.bharadwaj/reels/</t>
+          <t>https://www.instagram.com/dr.atulbothra/reels/</t>
         </is>
       </c>
     </row>
